--- a/reports/pdf_rolling5_20260904.xlsx
+++ b/reports/pdf_rolling5_20260904.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,425억   ·   현금 71억(1.6%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 9종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,314억   ·   현금 47억(1.1%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 9종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>146</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1754956500</v>
+        <v>1749810000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-111</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-7301457900</v>
+        <v>-7280046000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1617669900</v>
+        <v>1612926000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-5067532800</v>
+        <v>-5052672000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2382771600</v>
+        <v>2375784000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-25</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1470562500</v>
+        <v>-1466250000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2423793900</v>
+        <v>2416686000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-21</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1032258150</v>
+        <v>-1029231000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3311962500</v>
+        <v>3302250000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-10</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1012770000</v>
+        <v>-1009800000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>769398300</v>
+        <v>767142000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-9</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2605581000</v>
+        <v>-2597940000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>854409600</v>
+        <v>851904000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-3</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1169289000</v>
+        <v>-1165860000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5986596000</v>
+        <v>5969040000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>878245500</v>
+        <v>875670000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,652억   ·   현금 36억(1.0%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,530억   ·   현금 24억(0.7%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1051,7 +1051,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,471억   ·   현금 94억(3.8%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 8종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,410억   ·   현금 62억(2.6%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 8종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1147,7 +1147,7 @@
         <v>333</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2327403600</v>
+        <v>2330766900</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>-92</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1298745600</v>
+        <v>-1300622400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>300</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1833108000</v>
+        <v>1835757000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>-70</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1167404000</v>
+        <v>-1169091000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>97</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>3369624800</v>
+        <v>3374494200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>-40</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1790896000</v>
+        <v>-1793484000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1356873600</v>
+        <v>1358834400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>-37</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-6529020000</v>
+        <v>-6538455000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1206986400</v>
+        <v>1208730600</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>-32</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-735180800</v>
+        <v>-736243200</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>16</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>4628096000</v>
+        <v>4634784000</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>-29</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-2004793200</v>
+        <v>-2007690300</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>470836800</v>
+        <v>471517200</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>-15</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1219650000</v>
+        <v>-1221412500</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>294792000</v>
+        <v>295218000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>-13</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1204564400</v>
+        <v>-1206305100</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,065억   ·   현금 75억(3.6%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 2종목  /  매도 7종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,990억   ·   현금 50억(2.5%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 2종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1588,7 +1588,7 @@
         <v>52</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2587187200</v>
+        <v>2556569600</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>-122</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1999946000</v>
+        <v>-1976278000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>18</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1138316400</v>
+        <v>1124845200</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>-119</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-322580440</v>
+        <v>-318762920</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>-80</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-605696000</v>
+        <v>-598528000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>-45</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-414472500</v>
+        <v>-409567500</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>-44</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-303388800</v>
+        <v>-299798400</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>-17</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-150257900</v>
+        <v>-148479700</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>-5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-26735800</v>
+        <v>-26419400</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 262억   ·   현금 4억(1.5%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 12종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 257억   ·   현금 3억(1.0%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 12종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1905,11 +1905,11 @@
         <v>89</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>120301300</v>
+        <v>115753400</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.05%→2.50%</t>
+          <t>2.01%→2.45%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1926,11 +1926,11 @@
         <v>-344</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-250432000</v>
+        <v>-243208000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>8.55%→7.56%</t>
+          <t>8.47%→7.49%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1949,11 +1949,11 @@
         <v>73</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>170674000</v>
+        <v>169652000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>6.34%→6.97%</t>
+          <t>6.42%→7.07%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1970,11 +1970,11 @@
         <v>-123</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-85755600</v>
+        <v>-83430900</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.26%→0.92%</t>
+          <t>1.25%→0.92%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1993,11 +1993,11 @@
         <v>47</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>51817500</v>
+        <v>51126600</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.49%</t>
+          <t>3.32%→3.51%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2014,11 +2014,11 @@
         <v>-72</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-62395200</v>
+        <v>-61790400</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.55%</t>
+          <t>2.83%→2.58%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2037,11 +2037,11 @@
         <v>40</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>140280000</v>
+        <v>138740000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.63%→1.17%</t>
+          <t>0.64%→1.18%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2058,11 +2058,11 @@
         <v>-32</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-131936000</v>
+        <v>-127008000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.22%→1.71%</t>
+          <t>2.18%→1.68%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2081,11 +2081,11 @@
         <v>30</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>55335000</v>
+        <v>51030000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.35%→2.56%</t>
+          <t>2.21%→2.40%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2102,11 +2102,11 @@
         <v>-32</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-46480000</v>
+        <v>-46368000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>5.55%→5.36%</t>
+          <t>5.65%→5.45%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2125,11 +2125,11 @@
         <v>29</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>68614000</v>
+        <v>69832000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>3.14%→3.40%</t>
+          <t>3.26%→3.53%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2146,7 +2146,7 @@
         <v>-15</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-33915000</v>
+        <v>-33285000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2169,11 +2169,11 @@
         <v>21</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>82026000</v>
+        <v>76293000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.89%→3.19%</t>
+          <t>2.74%→3.03%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2190,11 +2190,11 @@
         <v>-11</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-30492000</v>
+        <v>-30569000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.72%</t>
+          <t>2.91%→2.79%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2213,11 +2213,11 @@
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>35385000</v>
+        <v>34387500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.22%</t>
+          <t>1.08%→1.21%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2234,11 +2234,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-35280000</v>
+        <v>-35140000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.43%→1.29%</t>
+          <t>1.45%→1.31%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2257,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>68208000</v>
+        <v>67228000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2278,11 +2278,11 @@
         <v>-7</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-24941000</v>
+        <v>-23765000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.18%→1.08%</t>
+          <t>1.15%→1.05%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2301,11 +2301,11 @@
         <v>11</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>24486000</v>
+        <v>23908500</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.15%→2.24%</t>
+          <t>2.14%→2.23%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2322,11 +2322,11 @@
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-4238500</v>
+        <v>-4042500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.53%→0.52%</t>
+          <t>0.52%→0.50%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>13167000</v>
+        <v>12915000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2359,23 +2359,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파마리서치  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-7423500</v>
+        <v>-80010000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.60%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>66→63</t>
+          <t>3→0</t>
         </is>
       </c>
     </row>
@@ -2389,11 +2389,11 @@
         <v>3</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>35595000</v>
+        <v>30912000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.23%</t>
+          <t>0.08%→0.20%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2403,30 +2403,30 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>파마리서치  (편출)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-82425000</v>
+        <v>-7098000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.00%</t>
+          <t>0.61%→0.58%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>3→0</t>
+          <t>66→63</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 523억   ·   현금 13억(2.5%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 9억(1.7%)      오늘 2026-09-04  vs  5일전 2026-08-28      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2522,7 +2522,7 @@
         <v>19</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>120843800</v>
+        <v>121867900</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>-234</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-532083240</v>
+        <v>-536592420</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>12</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>539496000</v>
+        <v>544068000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>-12</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-652068000</v>
+        <v>-657594000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>198700200</v>
+        <v>200384100</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>100182000</v>
+        <v>101031000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260904.xlsx
+++ b/reports/pdf_rolling5_20260904.xlsx
@@ -2271,23 +2271,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-23765000</v>
+        <v>-4042500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.15%→1.05%</t>
+          <t>0.52%→0.50%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>
@@ -2315,23 +2315,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-4042500</v>
+        <v>-23765000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.50%</t>
+          <t>1.15%→1.05%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260904.xlsx
+++ b/reports/pdf_rolling5_20260904.xlsx
@@ -2271,23 +2271,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-4042500</v>
+        <v>-23765000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.50%</t>
+          <t>1.15%→1.05%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>
@@ -2315,23 +2315,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-23765000</v>
+        <v>-4042500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.15%→1.05%</t>
+          <t>0.52%→0.50%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260904.xlsx
+++ b/reports/pdf_rolling5_20260904.xlsx
@@ -2271,23 +2271,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-23765000</v>
+        <v>-4042500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.15%→1.05%</t>
+          <t>0.52%→0.50%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>
@@ -2315,23 +2315,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-4042500</v>
+        <v>-23765000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.50%</t>
+          <t>1.15%→1.05%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>
@@ -2359,23 +2359,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>파마리서치  (편출)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-80010000</v>
+        <v>-7098000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.00%</t>
+          <t>0.61%→0.58%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>3→0</t>
+          <t>66→63</t>
         </is>
       </c>
     </row>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파마리서치  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-7098000</v>
+        <v>-80010000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.58%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>66→63</t>
+          <t>3→0</t>
         </is>
       </c>
     </row>
